--- a/testing/Cameo global/2024-25/Cameo_Global_Full_Statement_PY_Variance.xlsx
+++ b/testing/Cameo global/2024-25/Cameo_Global_Full_Statement_PY_Variance.xlsx
@@ -480,12 +480,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="330" customWidth="1" min="3" max="3"/>
+    <col width="328" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -502,7 +502,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Line Items Reconciled: 128 | Matched: 92 | Mismatches: 36</t>
+          <t>Total Line Items Reconciled: 126 | Matched: 92 | Mismatches: 34</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fotal outstanding dues of creditors other than micro enterprises &amp; small enterprises</t>
+          <t>Total outstanding dues of creditors other than micro enterprises &amp; small enterprises</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rade receivables</t>
+          <t>Trade receivables</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -845,7 +845,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ash and cash equivalents</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hort-term loans and advances</t>
+          <t>Short-term loans and advances</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -903,7 +903,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ther current assets</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -1139,17 +1139,17 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>66583070.00000001</v>
+        <v>110340810</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>110340810</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-43757740</v>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>48863980</v>
+        <v>80890980</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>80890980</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-32027000</v>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Cash Flow Statement</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1867,10 +1867,10 @@
         <v>10000000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>9999000</v>
+        <v>9997000</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>re capital at the beginning of the period</t>
+          <t>Share capital at the beginning of the period</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
@@ -1918,21 +1918,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>apital at the end of the period</t>
+          <t>Share capital at the end of the period</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
         <v>500000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-4500000</v>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2179,21 +2179,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Advances from customers</t>
+          <t>Previous Year</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>139358260</v>
+        <v>20000000</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>139358260</v>
+        <v>2048440</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>17951560</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2203,26 +2203,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Payables to employees</t>
+          <t>Not billed</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>375280</v>
+        <v>0</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>375280</v>
+        <v>2023000</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-2023000</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2232,19 +2232,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Statutory Dues</t>
+          <t>Not due</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>7486670</v>
+        <v>0</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>7486670</v>
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>0</v>
@@ -2261,26 +2261,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Income Tax Payable</t>
+          <t>Less than 6 months</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>19215910</v>
+        <v>0</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>11985020</v>
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>7230890</v>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2290,26 +2290,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Provision for compensated absences</t>
+          <t>6 months - 1 year</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>206240</v>
+        <v>0</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>670014000</v>
+        <v>0</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>-669807760</v>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2319,19 +2319,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Provision for gratuity (net)</t>
+          <t>1 - 2 year</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>644290</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>644290</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>0</v>
@@ -2348,26 +2348,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Provision for expenses</t>
+          <t>2 - 3 year</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>2476280</v>
+        <v>0</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2476280</v>
+        <v>2630</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-2630</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Previous Year</t>
+          <t>More than 3 years</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2048440</v>
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>17951560</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2406,26 +2406,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Not billed</t>
+          <t>In current accounts</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>0</v>
+        <v>33292680</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>45940910</v>
+        <v>33292680</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>-45940910</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2435,19 +2435,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Not due</t>
+          <t>In deposit accounts</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0</v>
+        <v>14809040</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0</v>
+        <v>14809040</v>
       </c>
       <c r="F70" s="4" t="n">
         <v>0</v>
@@ -2464,19 +2464,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Less than 6 months</t>
+          <t>Prepaid expenses - Unsecured, considered good</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>0</v>
+        <v>4843040</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0</v>
+        <v>4843040</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>0</v>
@@ -2493,19 +2493,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>6 months - 1 year</t>
+          <t>GST Credit</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>0</v>
+        <v>51571960</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0</v>
+        <v>51571960</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>0</v>
@@ -2522,19 +2522,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1 - 2 year</t>
+          <t>Advances paid to creditors</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>0</v>
+        <v>7150450</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0</v>
+        <v>7150450</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>0</v>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2 - 3 year</t>
+          <t>Income tax refund</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>0</v>
+        <v>7230890</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2630</v>
+        <v>-29449830</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-2630</v>
+        <v>36680720</v>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
@@ -2580,19 +2580,19 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Notes ((Amount in thousands ) 10. Other non-cur)</t>
+          <t>Notes (Notes forming part of the financial stat)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>More than 3 years</t>
+          <t>Insurance Wallet</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>0</v>
+        <v>222300</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0</v>
+        <v>222300</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>0</v>
@@ -2614,14 +2614,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>In current accounts</t>
+          <t>Other recoverable</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>33292680</v>
+        <v>2339780</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>33292680</v>
+        <v>2339780</v>
       </c>
       <c r="F76" s="4" t="n">
         <v>0</v>
@@ -2643,14 +2643,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>In deposit accounts</t>
+          <t>Less: Provision for other recoverable</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>14809040</v>
+        <v>-2339780</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>14809040</v>
+        <v>-2339780</v>
       </c>
       <c r="F77" s="4" t="n">
         <v>0</v>
@@ -2672,17 +2672,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prepaid expenses - Unsecured, considered good</t>
+          <t>Revenue from operations</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>4843040</v>
+        <v>739154000</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>4843040</v>
+        <v>739154810</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0</v>
+        <v>-810</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -2701,17 +2701,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GST Credit</t>
+          <t>- Fixed Deposits</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>51571960</v>
+        <v>1228000</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>51571960</v>
+        <v>1228080</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -2730,21 +2730,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Advances paid to creditors</t>
+          <t>Net Gain on the account of Foreign Exchange fluctuations Rental Income</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>7150450</v>
+        <v>71000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>7150450</v>
+        <v>2967210</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-2896210</v>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Income tax refund</t>
+          <t>Gratuity Expense</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>7230890</v>
+        <v>7100300</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>-29449830</v>
+        <v>445737620</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>36680720</v>
+        <v>-438637320</v>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
@@ -2788,17 +2788,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Insurance Wallet</t>
+          <t>Leave Encashment</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>222300</v>
+        <v>5165800</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>222300</v>
+        <v>5165860</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
@@ -2817,17 +2817,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Other recoverable</t>
+          <t>Contribution to Provident &amp; Other Funds</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>2339780</v>
+        <v>11448700</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2339780</v>
+        <v>11448760</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Less: Provision for other recoverable</t>
+          <t>Depreciation of Property, Plant and Equipment, Plant and Equipment  Less: Depreciation on revaluation increase transferred from revaluation reserve:</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-2339780</v>
+        <v>6491900</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-2339780</v>
+        <v>7703690</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-1211790</v>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2875,21 +2875,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Revenue from operations</t>
+          <t>Amortization of Intangible assets assets</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>739154000</v>
+        <v>1916500</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>739154810</v>
+        <v>7075490</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>-810</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-5158990</v>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2904,21 +2904,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>- Fixed Deposits</t>
+          <t>Impairment of goodwill</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>1228000</v>
+        <v>1510500</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1228080</v>
+        <v>-2209740</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-80</v>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>3720240</v>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -2933,21 +2933,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Net Gain on the account of Foreign Exchange fluctuations Rental Income</t>
+          <t>Professional Charges</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>71000</v>
+        <v>135311900</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2967210</v>
+        <v>135311940</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>-2896210</v>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>-40</v>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2962,21 +2962,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gratuity Expense</t>
+          <t>Facility Costs, Repairs &amp; Maintenance</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>7100300</v>
+        <v>21144900</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>445737620</v>
+        <v>21144960</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-438637320</v>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>-60</v>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -2991,21 +2991,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>eave Encashment</t>
+          <t>Rates and Taxes</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>5165800</v>
+        <v>5125500</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>5165860</v>
+        <v>4272630</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>852870</v>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3020,21 +3020,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Contribution to Provident &amp; Other Funds</t>
+          <t>Recruitment and hiring charges</t>
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>11448700</v>
+        <v>1436300</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>11448760</v>
+        <v>135311940</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-133875640</v>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3049,21 +3049,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>epreciation of Property, Plant and Equipment  Less: Depreciation on revaluation increase transferred from revaluation reserve:</t>
+          <t>Telephone &amp; Internet Charges</t>
         </is>
       </c>
       <c r="D91" s="4" t="n">
-        <v>6491900</v>
+        <v>1395500</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>7703690</v>
+        <v>1395560</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>-1211790</v>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>-60</v>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3078,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mortization of Intangible assets</t>
+          <t>Office Expenses</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1916500</v>
+        <v>1314900</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>7075490</v>
+        <v>177635120</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-5158990</v>
+        <v>-176320220</v>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
@@ -3102,26 +3102,26 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>npairment of goodwill</t>
+          <t>Earnings in Foreign Currency</t>
         </is>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1510500</v>
+        <v>610232840</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>-2209740</v>
+        <v>610232840</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>3720240</v>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3131,26 +3131,26 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>rofessional Charges</t>
+          <t>Contingent liabilities  (a) GST Order  During April 2023, the company received a GST order for FY 2019-20, assessing tax liability of INR 15.51 Lakhs along with an interest and penalty demand of INR 11.33 Lakhs. The tax liability has been settled through the Electronic Credit Ledger. This order has been dropped in FY 24-25.</t>
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>135311900</v>
+        <v>1133160</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>135311940</v>
+        <v>-29449830</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>30582990</v>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3160,22 +3160,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ncility Costs\nepairs &amp; maintenance</t>
+          <t>Microcom Solutions Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>21144900</v>
+        <v>1646890</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>21144960</v>
+        <v>1646890</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -3189,26 +3189,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ates and Taxes</t>
+          <t>Globconverinc Technology System India Private Limited*</t>
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>5125500</v>
+        <v>15740740</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>4272630</v>
+        <v>15740740</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>852870</v>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3218,26 +3218,26 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ecruitment and hiring charges</t>
+          <t>Aptude Technology Services SDN BHD</t>
         </is>
       </c>
       <c r="D97" s="4" t="n">
-        <v>1436300</v>
+        <v>16880180</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>135311940</v>
+        <v>16880180</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>-133875640</v>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3247,22 +3247,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>elephone &amp; Internet Charges</t>
+          <t>Aptude LLC*</t>
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1395500</v>
+        <v>396578470</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1395560</v>
+        <v>396578470</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
@@ -3276,26 +3276,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Notes (Notes forming part of the financial stat)</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>fice Expenses</t>
+          <t>Cameo Global Inc, USA*</t>
         </is>
       </c>
       <c r="D99" s="4" t="n">
-        <v>1314900</v>
+        <v>196774190</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>177635120</v>
+        <v>196774190</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>-176320220</v>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3310,14 +3310,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Earnings in Foreign Currency</t>
+          <t>Cameo Global Inc, USA - Advance from customers</t>
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>610232840</v>
+        <v>126259500</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>610232840</v>
+        <v>126259500</v>
       </c>
       <c r="F100" s="4" t="n">
         <v>0</v>
@@ -3339,21 +3339,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Contingent liabilities  (a) GST Order  **During April 2023, the company received a GST order for FY 2019-20, assessing tax liability of INR 15.51 Lakhs along with an interest and penalty demand of INR 11.33 Lakhs. The tax liability has been settled through the Electronic Credit Ledger. This order has been dropped in FY 24-25.</t>
+          <t>Globconverinc Technology System India Private Limited - Advance from customers</t>
         </is>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1133160</v>
+        <v>13098760</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>-29449830</v>
+        <v>13098760</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>30582990</v>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3368,21 +3368,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Microcom Solutions Pvt. Ltd.</t>
+          <t>Aptude LLC - Trade Receivable</t>
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1646890</v>
+        <v>32122900</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1646890</v>
+        <v>2023000</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>30099900</v>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3397,21 +3397,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Globconverinc Technology System India Private Limited*</t>
+          <t>Microcom Solutions Pvt. Ltd. - Advances paid to creditors</t>
         </is>
       </c>
       <c r="D103" s="4" t="n">
-        <v>15740740</v>
+        <v>240470</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>15740740</v>
+        <v>51571960</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-51331490</v>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3426,21 +3426,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Aptude Technology Services SDN BHD</t>
+          <t>Net profit/(loss) attributable to Equity Shareholders for the period</t>
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>16880180</v>
+        <v>80890980</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>16880180</v>
+        <v>80890982000</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-80810091020</v>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3455,21 +3455,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Aptude LLC*</t>
+          <t>calculation of basic earnings per share</t>
         </is>
       </c>
       <c r="D105" s="4" t="n">
-        <v>396578470</v>
+        <v>5000</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>396578470</v>
+        <v>5000000</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-4995000</v>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3484,14 +3484,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cameo Global Inc, USA*</t>
+          <t>Earning/(loss) per share, Basic (in INR)</t>
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>196774190</v>
+        <v>16178200</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>196774190</v>
+        <v>16178200</v>
       </c>
       <c r="F106" s="4" t="n">
         <v>0</v>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cameo Global Inc</t>
+          <t>Adjusted profit/(loss) for calculation of diluted EPS</t>
         </is>
       </c>
       <c r="D107" s="4" t="n">
-        <v>0</v>
+        <v>80890980</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>4000000</v>
+        <v>80890982000</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>-4000000</v>
+        <v>-80810091020</v>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Net profit/(loss) attributable to Equity Shareholders for the period</t>
+          <t>Weighted average number of equity shares (subscribed) used for&lt;br&gt;Weighted average number of equity shares resulting from conversion of&lt;br&gt;Financial instruments</t>
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>80890980</v>
+        <v>5000</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>80890982000</v>
+        <v>5000000</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-80810091020</v>
+        <v>-4995000</v>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
@@ -3571,21 +3571,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Earning/(loss) per share, Basic (in INR)</t>
+          <t>calculation of diluted earnings per share</t>
         </is>
       </c>
       <c r="D109" s="4" t="n">
-        <v>16178200</v>
+        <v>5000</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>16178200</v>
+        <v>5000000</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-4995000</v>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3595,26 +3595,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Statement of Profit and Loss</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Adjusted profit/(loss) for calculation of diluted EPS</t>
+          <t>Earning/(loss) per share, Diluted (in INR)</t>
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>80890980</v>
+        <v>16178200</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>80890982000</v>
+        <v>16178200</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-80810091020</v>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3629,14 +3629,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Earning/(loss) per share, Diluted (in INR)</t>
+          <t>Net defined benefit liability, gratuity plan</t>
         </is>
       </c>
       <c r="D111" s="4" t="n">
-        <v>16178200</v>
+        <v>18629730</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>16178200</v>
+        <v>18629730</v>
       </c>
       <c r="F111" s="4" t="n">
         <v>0</v>
@@ -3658,21 +3658,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Net defined benefit liability, gratuity plan</t>
+          <t>Liability for compensated absences</t>
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>18629730</v>
+        <v>6994380</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>18629730</v>
+        <v>670014000</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-663019620</v>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3687,21 +3687,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Liability for compensated absences</t>
+          <t>Total employee benefit liability</t>
         </is>
       </c>
       <c r="D113" s="4" t="n">
-        <v>6994380</v>
+        <v>25624110</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>670014000</v>
+        <v>25624110</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>-663019620</v>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Total employee benefit liability</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>25624110</v>
+        <v>36204410</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>25624110</v>
+        <v>36204410</v>
       </c>
       <c r="F114" s="4" t="n">
         <v>0</v>
@@ -3745,14 +3745,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Non-current</t>
+          <t>Obligation at the beginning of the year</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
-        <v>36204410</v>
+        <v>25736820</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>36204410</v>
+        <v>25736820</v>
       </c>
       <c r="F115" s="4" t="n">
         <v>0</v>
@@ -3774,21 +3774,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Obligation at the beginning of the year</t>
+          <t>Past service cost (Vested employees)</t>
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>25736820</v>
+        <v>0</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>25736820</v>
+        <v>6317120</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-6317120</v>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -3861,21 +3861,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prior Year Change</t>
+          <t>Benefits settled</t>
         </is>
       </c>
       <c r="D119" s="4" t="n">
-        <v>0</v>
+        <v>-3633760</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>4000</v>
+        <v>-3633760</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -3890,14 +3890,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Benefits settled</t>
+          <t>Actuarial (Gain) / Loss on the Obligation</t>
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-3633760</v>
+        <v>-261570</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-3633760</v>
+        <v>-261570</v>
       </c>
       <c r="F120" s="4" t="n">
         <v>0</v>
@@ -3919,14 +3919,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Actuarial (Gain) / Loss on the Obligation</t>
+          <t>Obligation at the end of the year</t>
         </is>
       </c>
       <c r="D121" s="4" t="n">
-        <v>-261570</v>
+        <v>30060560</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>-261570</v>
+        <v>30060560</v>
       </c>
       <c r="F121" s="4" t="n">
         <v>0</v>
@@ -3948,14 +3948,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Obligation at the end of the year</t>
+          <t>Plan assets at the beginning of the year, at fair value</t>
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>30060560</v>
+        <v>-8339020</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>30060560</v>
+        <v>-8339020</v>
       </c>
       <c r="F122" s="4" t="n">
         <v>0</v>
@@ -3977,14 +3977,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Plan assets at the beginning of the year, at fair value</t>
+          <t>Interest income on plan assets</t>
         </is>
       </c>
       <c r="D123" s="4" t="n">
-        <v>-8339020</v>
+        <v>-639600</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>-8339020</v>
+        <v>-639600</v>
       </c>
       <c r="F123" s="4" t="n">
         <v>0</v>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Interest income on plan assets</t>
+          <t>Remeasurement- actuarial gain/(loss)</t>
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-639600</v>
+        <v>-217600</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-639600</v>
+        <v>-217600</v>
       </c>
       <c r="F124" s="4" t="n">
         <v>0</v>
@@ -4035,21 +4035,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remeasurement- actuarial gain/(loss)</t>
+          <t>Return on plan assets recognized in other comprehensive income</t>
         </is>
       </c>
       <c r="D125" s="4" t="n">
-        <v>-217600</v>
+        <v>0</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>-217600</v>
+        <v>7075490</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-7075490</v>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -4064,21 +4064,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Return on plan assets recognized in other comprehensive income</t>
+          <t>Plan assets as at the end of the year</t>
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>0</v>
+        <v>-11430830</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>7075490</v>
+        <v>-11430830</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-7075490</v>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -4093,14 +4093,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Plan assets as at the end of the year</t>
+          <t>Net defined benefit liability</t>
         </is>
       </c>
       <c r="D127" s="4" t="n">
-        <v>-11430830</v>
+        <v>18629730</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>-11430830</v>
+        <v>18629730</v>
       </c>
       <c r="F127" s="4" t="n">
         <v>0</v>
@@ -4122,21 +4122,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Net defined benefit liability</t>
+          <t>Past service cost (Unvested employees)</t>
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>18629730</v>
+        <v>0</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>18629730</v>
+        <v>6317120</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
+        <v>-6317120</v>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
     </row>
@@ -4151,21 +4151,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Past service cost (Vested employees)</t>
+          <t>Net Actuarial (Gain) / Loss recognized in the period</t>
         </is>
       </c>
       <c r="D129" s="4" t="n">
-        <v>0</v>
+        <v>-1118770</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>6317120</v>
+        <v>-1118770</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>-6317120</v>
-      </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
         </is>
       </c>
     </row>
@@ -4180,77 +4180,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Past service cost (Unvested employees)</t>
+          <t>Net gratuity cost/ Leave encashment cost</t>
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0</v>
+        <v>7100300</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>6317120</v>
+        <v>7100300</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-6317120</v>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>127</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Statement of Profit and Loss</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Net Actuarial (Gain) / Loss recognized in the period</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>-1118770</v>
-      </c>
-      <c r="E131" s="4" t="n">
-        <v>-1118770</v>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>MATCHED</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>128</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Statement of Profit and Loss</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Net gratuity cost/ Leave encashment cost</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="n">
-        <v>7100300</v>
-      </c>
-      <c r="E132" s="4" t="n">
-        <v>7100300</v>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>MATCHED</t>
         </is>
